--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_JAEN PARAISO INTERIOR FS.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_JAEN PARAISO INTERIOR FS.xlsx
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>12.8518</v>
+        <v>17.9995</v>
       </c>
       <c r="E2" t="n">
-        <v>10.9566</v>
+        <v>15.5728</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8952</v>
+        <v>2.4267</v>
       </c>
       <c r="G2" t="n">
-        <v>4.905200000000001</v>
+        <v>2.427</v>
       </c>
       <c r="H2" t="n">
-        <v>5.3665</v>
+        <v>2.4086</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4612</v>
+        <v>0.01839999999999975</v>
       </c>
       <c r="J2" t="n">
-        <v>6.9947</v>
+        <v>6.9342</v>
       </c>
       <c r="K2" t="n">
-        <v>5.511100000000001</v>
+        <v>4.2265</v>
       </c>
       <c r="L2" t="n">
-        <v>1.4836</v>
+        <v>2.7075</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.0894</v>
+        <v>-4.5071</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1446</v>
+        <v>-1.8181</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.9449</v>
+        <v>-2.6892</v>
       </c>
       <c r="P2" t="n">
-        <v>4.0012</v>
+        <v>2.1421</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-5.0632</v>
       </c>
       <c r="R2" t="n">
-        <v>4.0012</v>
+        <v>7.2052</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6262</v>
+        <v>6.5899</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0428</v>
+        <v>5.6919</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5834</v>
+        <v>0.8983</v>
       </c>
       <c r="V2" t="n">
-        <v>2.3193</v>
+        <v>6.8407</v>
       </c>
       <c r="W2" t="n">
-        <v>2.9192</v>
+        <v>8.0101</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.5999</v>
+        <v>-1.1695</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. JUZBASIC</t>
+          <t>J. VALEIRAS CREUS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>10.6456</v>
+        <v>17.8254</v>
       </c>
       <c r="E3" t="n">
-        <v>7.617900000000001</v>
+        <v>18.4739</v>
       </c>
       <c r="F3" t="n">
-        <v>3.0278</v>
+        <v>-0.6484000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>6.913399999999999</v>
+        <v>7.4657</v>
       </c>
       <c r="H3" t="n">
-        <v>5.333</v>
+        <v>1.6568</v>
       </c>
       <c r="I3" t="n">
-        <v>1.5804</v>
+        <v>5.809</v>
       </c>
       <c r="J3" t="n">
-        <v>7.1457</v>
+        <v>12.3176</v>
       </c>
       <c r="K3" t="n">
-        <v>5.2204</v>
+        <v>5.7195</v>
       </c>
       <c r="L3" t="n">
-        <v>1.9255</v>
+        <v>6.598</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2323999999999999</v>
+        <v>-4.8518</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1128</v>
+        <v>-4.0628</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3451</v>
+        <v>-0.7890999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-0.5842999999999999</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.0009</v>
+        <v>-7.4</v>
       </c>
       <c r="R3" t="n">
-        <v>3.0009</v>
+        <v>6.8159</v>
       </c>
       <c r="S3" t="n">
-        <v>3.2126</v>
+        <v>8.450200000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>1.9141</v>
+        <v>7.5027</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2984</v>
+        <v>0.9477</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5196000000000001</v>
+        <v>2.4937</v>
       </c>
       <c r="W3" t="n">
-        <v>1.5588</v>
+        <v>6.0538</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0392</v>
+        <v>-3.5601</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. BOTAS FERNANDEZ</t>
+          <t>S. MELERO ZURITA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>7.703900000000001</v>
+        <v>15.68</v>
       </c>
       <c r="E4" t="n">
-        <v>6.1525</v>
+        <v>16.305</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5514</v>
+        <v>-0.625</v>
       </c>
       <c r="G4" t="n">
-        <v>1.9631</v>
+        <v>6.081799999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>3.5989</v>
+        <v>1.6015</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.636</v>
+        <v>4.4806</v>
       </c>
       <c r="J4" t="n">
-        <v>4.9811</v>
+        <v>9.326000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>3.7297</v>
+        <v>2.8406</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2512</v>
+        <v>6.4855</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.018</v>
+        <v>-3.2441</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1308</v>
+        <v>-1.2391</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.8872</v>
+        <v>-2.0049</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8003</v>
+        <v>1.1684</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4.0012</v>
+        <v>-5.2579</v>
       </c>
       <c r="R4" t="n">
-        <v>4.801299999999999</v>
+        <v>6.4264</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1415999999999999</v>
+        <v>0.5658999999999998</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1137</v>
+        <v>0.3573</v>
       </c>
       <c r="U4" t="n">
-        <v>0.02790000000000001</v>
+        <v>0.2087000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>4.7991</v>
+        <v>7.8637</v>
       </c>
       <c r="W4" t="n">
-        <v>5.0589</v>
+        <v>11.8795</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2598</v>
+        <v>-4.016</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. SALAS MERCHAN</t>
+          <t>D. JUZBASIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>6.787000000000001</v>
+        <v>12.0699</v>
       </c>
       <c r="E5" t="n">
-        <v>5.985799999999999</v>
+        <v>9.8758</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8012</v>
+        <v>2.1939</v>
       </c>
       <c r="G5" t="n">
-        <v>1.7452</v>
+        <v>4.6675</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9502999999999999</v>
+        <v>1.8533</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7949000000000001</v>
+        <v>2.8142</v>
       </c>
       <c r="J5" t="n">
-        <v>2.876</v>
+        <v>9.7537</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0305</v>
+        <v>3.9977</v>
       </c>
       <c r="L5" t="n">
-        <v>1.8454</v>
+        <v>5.756</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.1308</v>
+        <v>-5.0862</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.08020000000000005</v>
+        <v>-2.1444</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.0505</v>
+        <v>-2.9418</v>
       </c>
       <c r="P5" t="n">
-        <v>2.4007</v>
+        <v>-2.3369</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-8.958</v>
       </c>
       <c r="R5" t="n">
-        <v>2.4007</v>
+        <v>6.6211</v>
       </c>
       <c r="S5" t="n">
-        <v>3.0209</v>
+        <v>6.1276</v>
       </c>
       <c r="T5" t="n">
-        <v>2.85</v>
+        <v>1.1731</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1708999999999999</v>
+        <v>4.9545</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3798</v>
+        <v>3.6115</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2598</v>
+        <v>7.9069</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6395999999999999</v>
+        <v>-4.2954</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. VALEIRAS CREUS</t>
+          <t>M. BOTAS FERNANDEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>6.5027</v>
+        <v>9.289899999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>7.107699999999999</v>
+        <v>5.6192</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6052</v>
+        <v>3.6707</v>
       </c>
       <c r="G6" t="n">
-        <v>4.8141</v>
+        <v>8.7944</v>
       </c>
       <c r="H6" t="n">
-        <v>3.2249</v>
+        <v>6.5316</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5892</v>
+        <v>2.2629</v>
       </c>
       <c r="J6" t="n">
-        <v>7.9238</v>
+        <v>13.1923</v>
       </c>
       <c r="K6" t="n">
-        <v>3.9625</v>
+        <v>7.8415</v>
       </c>
       <c r="L6" t="n">
-        <v>3.9613</v>
+        <v>5.3508</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.1097</v>
+        <v>-4.3979</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7376</v>
+        <v>-1.3101</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.3723</v>
+        <v>-3.0878</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.4001</v>
+        <v>-3.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.0012</v>
+        <v>-12.0736</v>
       </c>
       <c r="R6" t="n">
-        <v>3.601</v>
+        <v>8.3736</v>
       </c>
       <c r="S6" t="n">
-        <v>1.4086</v>
+        <v>-2.2409</v>
       </c>
       <c r="T6" t="n">
-        <v>1.9854</v>
+        <v>-1.5532</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5768000000000001</v>
+        <v>-0.6878000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6801999999999999</v>
+        <v>6.4363</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1998</v>
+        <v>6.0537</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5196</v>
+        <v>0.3826</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. MELERO ZURITA</t>
+          <t>R. SALAS MERCHAN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>4.5704</v>
+        <v>8.2784</v>
       </c>
       <c r="E7" t="n">
-        <v>6.1619</v>
+        <v>9.3597</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.5915</v>
+        <v>-1.0813</v>
       </c>
       <c r="G7" t="n">
-        <v>2.6945</v>
+        <v>6.3305</v>
       </c>
       <c r="H7" t="n">
-        <v>2.2644</v>
+        <v>3.3149</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4301000000000001</v>
+        <v>3.0156</v>
       </c>
       <c r="J7" t="n">
-        <v>3.7198</v>
+        <v>10.5063</v>
       </c>
       <c r="K7" t="n">
-        <v>2.1448</v>
+        <v>6.063099999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>1.575</v>
+        <v>4.443099999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.0253</v>
+        <v>-4.1757</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1197</v>
+        <v>-2.7484</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.145</v>
+        <v>-1.4274</v>
       </c>
       <c r="P7" t="n">
-        <v>2.8008</v>
+        <v>0.3894000000000002</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0003</v>
+        <v>-4.2842</v>
       </c>
       <c r="R7" t="n">
-        <v>3.8011</v>
+        <v>4.6736</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7945</v>
+        <v>5.2921</v>
       </c>
       <c r="T7" t="n">
-        <v>1.0428</v>
+        <v>2.3508</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2483</v>
+        <v>2.9414</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.7193</v>
+        <v>-3.7337</v>
       </c>
       <c r="W7" t="n">
-        <v>2.3995</v>
+        <v>0.7869000000000002</v>
       </c>
       <c r="X7" t="n">
-        <v>-4.1189</v>
+        <v>-4.5206</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. SIGISMONTI RODRIGUEZ</t>
+          <t>P. TRUÑO SOMS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>4.5038</v>
+        <v>5.7869</v>
       </c>
       <c r="E8" t="n">
-        <v>1.2449</v>
+        <v>5.7869</v>
       </c>
       <c r="F8" t="n">
-        <v>3.2588</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1.9266</v>
+        <v>5.7869</v>
       </c>
       <c r="H8" t="n">
-        <v>3.2214</v>
+        <v>0.9237</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.2946</v>
+        <v>4.8632</v>
       </c>
       <c r="J8" t="n">
-        <v>1.6945</v>
+        <v>5.7869</v>
       </c>
       <c r="K8" t="n">
-        <v>3.1591</v>
+        <v>0.9237</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.4646</v>
+        <v>4.8632</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2321</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0.06220000000000003</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1698999999999999</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2006</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.0006</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>4.2012</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9036</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2487</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6549</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2801</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.7997</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5196</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. TRUNO SOMS</t>
+          <t>P. ÁVALOS ORTIZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>1.9189</v>
+        <v>3.0553</v>
       </c>
       <c r="E9" t="n">
-        <v>0.08689999999999998</v>
+        <v>3.0553</v>
       </c>
       <c r="F9" t="n">
-        <v>1.8321</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1.6321</v>
+        <v>3.0553</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3268</v>
+        <v>1.2316</v>
       </c>
       <c r="I9" t="n">
-        <v>1.3053</v>
+        <v>1.8237</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6071</v>
+        <v>3.0553</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4070999999999999</v>
+        <v>1.2316</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2</v>
+        <v>1.8237</v>
       </c>
       <c r="M9" t="n">
-        <v>1.0251</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.08030000000000001</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1.1054</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.2001</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.0006</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8005</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.006900000000000128</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8804999999999999</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8735000000000001</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>0.4799</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5999</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. ÁVALOS ORTIZ</t>
+          <t>L. SIGISMONTI RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,34 +1186,34 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>1.7996</v>
+        <v>1.5395</v>
       </c>
       <c r="E10" t="n">
-        <v>1.7996</v>
+        <v>1.5395</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>1.7996</v>
+        <v>1.5395</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5998</v>
+        <v>1.5395</v>
       </c>
       <c r="I10" t="n">
-        <v>1.1998</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1.7996</v>
+        <v>1.5395</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5998</v>
+        <v>1.5395</v>
       </c>
       <c r="L10" t="n">
-        <v>1.1998</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>L. SIGISMONTI RODRÍGUEZ</t>
+          <t>D. JIMENEZ EXPOSITO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2999</v>
+        <v>-0.632</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2999</v>
+        <v>-0.7675999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>0.1357</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2999</v>
+        <v>-0.7834</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2999</v>
+        <v>0.0205</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>-0.804</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2999</v>
+        <v>-0.644</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2999</v>
+        <v>0.0205</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-0.6645</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>-0.1395</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>-0.1395</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>0.3895</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>0.3895</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-0.238</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>-0.1237</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>-0.1144</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P. TRUÑO SOMS</t>
+          <t>P. TRUNO SOMS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2999</v>
+        <v>-1.4231</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2999</v>
+        <v>-2.6568</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1.2337</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2999</v>
+        <v>-1.2834</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2999</v>
+        <v>-0.4542999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>-0.829</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2999</v>
+        <v>1.5134</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2999</v>
+        <v>2.6558</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>-1.1424</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>-2.7966</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>-3.1101</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>0.3134</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>0.1948</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-4.2842</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>4.4789</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-1.0509</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>-0.7245</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>-0.3262999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.7163</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.8384000000000001</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-0.1221</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. JIMENEZ EXPOSITO</t>
+          <t>J. CEBOLLA HERRERA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,70 +1420,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.6318</v>
+        <v>-1.5638</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.7869</v>
+        <v>0.1331999999999995</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1551</v>
+        <v>-1.6971</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.7867</v>
+        <v>2.6735</v>
       </c>
       <c r="H13" t="n">
-        <v>0.02</v>
+        <v>-0.1194</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.8067</v>
+        <v>2.7927</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.658</v>
+        <v>3.4522</v>
       </c>
       <c r="K13" t="n">
-        <v>0.02</v>
+        <v>1.2778</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.678</v>
+        <v>2.1742</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.1287</v>
+        <v>-0.7785</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>-1.3971</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1287</v>
+        <v>0.6185</v>
       </c>
       <c r="P13" t="n">
-        <v>0.4001</v>
+        <v>-1.3632</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-3.8948</v>
       </c>
       <c r="R13" t="n">
-        <v>0.4001</v>
+        <v>2.5315</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2452</v>
+        <v>-2.1415</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1289</v>
+        <v>-2.1457</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1163</v>
+        <v>0.00430000000000004</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>-0.7326999999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2.7216</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-3.4542</v>
       </c>
     </row>
     <row r="14">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.487</v>
+        <v>-3.391</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.8746</v>
+        <v>-1.0882</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.6124</v>
+        <v>-2.3027</v>
       </c>
       <c r="G14" t="n">
-        <v>-4.4948</v>
+        <v>-4.7278</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.9577</v>
+        <v>-2.205</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.5371</v>
+        <v>-2.5227</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.9847</v>
+        <v>-2.3205</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.7487</v>
+        <v>-1.883</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.236</v>
+        <v>-0.4375</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.5101</v>
+        <v>-2.4075</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.209</v>
+        <v>-0.3221</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.3011</v>
+        <v>-2.0854</v>
       </c>
       <c r="P14" t="n">
-        <v>0.4001</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.0003</v>
+        <v>-4.2842</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4004</v>
+        <v>3.7</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.072</v>
+        <v>-2.5099</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.889</v>
+        <v>-0.8168000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.183</v>
+        <v>-1.6932</v>
       </c>
       <c r="V14" t="n">
-        <v>1.6797</v>
+        <v>4.431</v>
       </c>
       <c r="W14" t="n">
-        <v>2.9994</v>
+        <v>6.3332</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.3198</v>
+        <v>-1.9022</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. CEBOLLA HERRERA</t>
+          <t>L. SIGISMONTI RODRIGUEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,70 +1576,70 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>-6.3611</v>
+        <v>-4.5162</v>
       </c>
       <c r="E15" t="n">
-        <v>-3.7837</v>
+        <v>-7.6769</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.5774</v>
+        <v>3.1607</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.8204</v>
+        <v>-4.6616</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3386</v>
+        <v>-0.6119999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.1589</v>
+        <v>-4.0496</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.7468</v>
+        <v>-1.5558</v>
       </c>
       <c r="K15" t="n">
-        <v>1.4396</v>
+        <v>2.2429</v>
       </c>
       <c r="L15" t="n">
-        <v>-2.1864</v>
+        <v>-3.7985</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.0736</v>
+        <v>-3.1058</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.101</v>
+        <v>-2.8548</v>
       </c>
       <c r="O15" t="n">
-        <v>0.02749999999999998</v>
+        <v>-0.2511000000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.4007</v>
+        <v>-1.5579</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.0009</v>
+        <v>-9.347300000000001</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6002000000000001</v>
+        <v>7.7895</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.2204</v>
+        <v>-0.739</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8956999999999999</v>
+        <v>-0.05430000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3246</v>
+        <v>-0.6846</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.9196</v>
+        <v>2.4422</v>
       </c>
       <c r="W15" t="n">
-        <v>0.8597</v>
+        <v>3.2806</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.7793</v>
+        <v>-0.8385</v>
       </c>
     </row>
     <row r="16">
@@ -1654,70 +1654,70 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>-6.7507</v>
+        <v>-20.4885</v>
       </c>
       <c r="E16" t="n">
-        <v>-7.0393</v>
+        <v>-19.2868</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2887</v>
+        <v>-1.2016</v>
       </c>
       <c r="G16" t="n">
-        <v>-6.54</v>
+        <v>-14.6878</v>
       </c>
       <c r="H16" t="n">
-        <v>-3.1111</v>
+        <v>-7.9009</v>
       </c>
       <c r="I16" t="n">
-        <v>-3.4288</v>
+        <v>-6.7869</v>
       </c>
       <c r="J16" t="n">
-        <v>-5.6367</v>
+        <v>-11.8174</v>
       </c>
       <c r="K16" t="n">
-        <v>-3.2446</v>
+        <v>-6.4447</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.392</v>
+        <v>-5.3727</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.9033</v>
+        <v>-2.8705</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1335</v>
+        <v>-1.4561</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.0368</v>
+        <v>-1.4142</v>
       </c>
       <c r="P16" t="n">
-        <v>2.0005</v>
+        <v>-2.9212</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0003</v>
+        <v>-8.179</v>
       </c>
       <c r="R16" t="n">
-        <v>3.0008</v>
+        <v>5.2578</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.0913</v>
+        <v>-2.7573</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6622</v>
+        <v>-1.0704</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.4291</v>
+        <v>-1.6869</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.12</v>
+        <v>-0.1221000000000001</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2598</v>
+        <v>1.78</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.3798</v>
+        <v>-1.9022</v>
       </c>
     </row>
     <row r="17">
@@ -1732,70 +1732,70 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>39.6529</v>
+        <v>59.51019999999998</v>
       </c>
       <c r="E17" t="n">
-        <v>34.2291</v>
+        <v>54.24499999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>5.4238</v>
+        <v>5.265300000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>16.35170000000001</v>
+        <v>22.67809999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>21.7756</v>
+        <v>9.790400000000002</v>
       </c>
       <c r="I17" t="n">
-        <v>-5.4236</v>
+        <v>12.8881</v>
       </c>
       <c r="J17" t="n">
-        <v>28.3159</v>
+        <v>61.0397</v>
       </c>
       <c r="K17" t="n">
-        <v>22.8311</v>
+        <v>32.25299999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>5.484799999999998</v>
+        <v>28.7864</v>
       </c>
       <c r="M17" t="n">
-        <v>-11.9641</v>
+        <v>-38.3612</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.0553</v>
+        <v>-22.4631</v>
       </c>
       <c r="O17" t="n">
-        <v>-10.9088</v>
+        <v>-15.8985</v>
       </c>
       <c r="P17" t="n">
-        <v>12.0034</v>
+        <v>-8.763500000000001</v>
       </c>
       <c r="Q17" t="n">
-        <v>-21.0063</v>
+        <v>-73.02640000000001</v>
       </c>
       <c r="R17" t="n">
-        <v>33.0094</v>
+        <v>64.26300000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>3.678799999999999</v>
+        <v>15.3482</v>
       </c>
       <c r="T17" t="n">
-        <v>7.004800000000001</v>
+        <v>10.5872</v>
       </c>
       <c r="U17" t="n">
-        <v>-3.3259</v>
+        <v>4.761700000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>7.619200000000001</v>
+        <v>30.2469</v>
       </c>
       <c r="W17" t="n">
-        <v>19.9145</v>
+        <v>55.64470000000001</v>
       </c>
       <c r="X17" t="n">
-        <v>-12.2955</v>
+        <v>-25.3982</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_JAEN PARAISO INTERIOR FS.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_JAEN PARAISO INTERIOR FS.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. MELERO ZURITA</t>
+          <t>S. MELERO ZURITA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>17.9995</v>
+        <v>15.711</v>
       </c>
       <c r="E2" t="n">
-        <v>15.5728</v>
+        <v>16.0299</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4267</v>
+        <v>-0.3190000000000002</v>
       </c>
       <c r="G2" t="n">
-        <v>2.427</v>
+        <v>6.081799999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>2.4086</v>
+        <v>1.6015</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01839999999999975</v>
+        <v>4.4806</v>
       </c>
       <c r="J2" t="n">
-        <v>6.9342</v>
+        <v>9.326000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>4.2265</v>
+        <v>2.8406</v>
       </c>
       <c r="L2" t="n">
-        <v>2.7075</v>
+        <v>6.4855</v>
       </c>
       <c r="M2" t="n">
-        <v>-4.5071</v>
+        <v>-3.2441</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.8181</v>
+        <v>-1.2391</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.6892</v>
+        <v>-2.0049</v>
       </c>
       <c r="P2" t="n">
-        <v>2.1421</v>
+        <v>1.1684</v>
       </c>
       <c r="Q2" t="n">
-        <v>-5.0632</v>
+        <v>-5.2579</v>
       </c>
       <c r="R2" t="n">
-        <v>7.2052</v>
+        <v>6.4264</v>
       </c>
       <c r="S2" t="n">
-        <v>6.5899</v>
+        <v>0.5969</v>
       </c>
       <c r="T2" t="n">
-        <v>5.6919</v>
+        <v>0.08219999999999997</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8983</v>
+        <v>0.5145999999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>6.8407</v>
+        <v>7.8637</v>
       </c>
       <c r="W2" t="n">
-        <v>8.0101</v>
+        <v>11.8795</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.1695</v>
+        <v>-4.016</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. VALEIRAS CREUS</t>
+          <t>D. MELERO ZURITA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>17.8254</v>
+        <v>15.316</v>
       </c>
       <c r="E3" t="n">
-        <v>18.4739</v>
+        <v>12.4072</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.6484000000000001</v>
+        <v>2.909</v>
       </c>
       <c r="G3" t="n">
-        <v>7.4657</v>
+        <v>2.427</v>
       </c>
       <c r="H3" t="n">
-        <v>1.6568</v>
+        <v>2.4086</v>
       </c>
       <c r="I3" t="n">
-        <v>5.809</v>
+        <v>0.01839999999999975</v>
       </c>
       <c r="J3" t="n">
-        <v>12.3176</v>
+        <v>6.9342</v>
       </c>
       <c r="K3" t="n">
-        <v>5.7195</v>
+        <v>4.2265</v>
       </c>
       <c r="L3" t="n">
-        <v>6.598</v>
+        <v>2.7075</v>
       </c>
       <c r="M3" t="n">
-        <v>-4.8518</v>
+        <v>-4.5071</v>
       </c>
       <c r="N3" t="n">
-        <v>-4.0628</v>
+        <v>-1.8181</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.7890999999999999</v>
+        <v>-2.6892</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.5842999999999999</v>
+        <v>2.1421</v>
       </c>
       <c r="Q3" t="n">
-        <v>-7.4</v>
+        <v>-5.0632</v>
       </c>
       <c r="R3" t="n">
-        <v>6.8159</v>
+        <v>7.2052</v>
       </c>
       <c r="S3" t="n">
-        <v>8.450200000000001</v>
+        <v>3.9064</v>
       </c>
       <c r="T3" t="n">
-        <v>7.5027</v>
+        <v>2.5261</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9477</v>
+        <v>1.3804</v>
       </c>
       <c r="V3" t="n">
-        <v>2.4937</v>
+        <v>6.8407</v>
       </c>
       <c r="W3" t="n">
-        <v>6.0538</v>
+        <v>8.0101</v>
       </c>
       <c r="X3" t="n">
-        <v>-3.5601</v>
+        <v>-1.1695</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. MELERO ZURITA</t>
+          <t>J. VALEIRAS CREUS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>15.68</v>
+        <v>14.8769</v>
       </c>
       <c r="E4" t="n">
-        <v>16.305</v>
+        <v>15.0091</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.625</v>
+        <v>-0.1320999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>6.081799999999999</v>
+        <v>7.4657</v>
       </c>
       <c r="H4" t="n">
-        <v>1.6015</v>
+        <v>1.6568</v>
       </c>
       <c r="I4" t="n">
-        <v>4.4806</v>
+        <v>5.809</v>
       </c>
       <c r="J4" t="n">
-        <v>9.326000000000001</v>
+        <v>12.3176</v>
       </c>
       <c r="K4" t="n">
-        <v>2.8406</v>
+        <v>5.7195</v>
       </c>
       <c r="L4" t="n">
-        <v>6.4855</v>
+        <v>6.598</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.2441</v>
+        <v>-4.8518</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.2391</v>
+        <v>-4.0628</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.0049</v>
+        <v>-0.7890999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1684</v>
+        <v>-0.5842999999999999</v>
       </c>
       <c r="Q4" t="n">
-        <v>-5.2579</v>
+        <v>-7.4</v>
       </c>
       <c r="R4" t="n">
-        <v>6.4264</v>
+        <v>6.8159</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5658999999999998</v>
+        <v>5.5017</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3573</v>
+        <v>4.0378</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2087000000000001</v>
+        <v>1.4639</v>
       </c>
       <c r="V4" t="n">
-        <v>7.8637</v>
+        <v>2.4937</v>
       </c>
       <c r="W4" t="n">
-        <v>11.8795</v>
+        <v>6.0538</v>
       </c>
       <c r="X4" t="n">
-        <v>-4.016</v>
+        <v>-3.5601</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. JUZBASIC</t>
+          <t>M. BOTAS FERNANDEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>12.0699</v>
+        <v>13.8421</v>
       </c>
       <c r="E5" t="n">
-        <v>9.8758</v>
+        <v>8.8329</v>
       </c>
       <c r="F5" t="n">
-        <v>2.1939</v>
+        <v>5.0092</v>
       </c>
       <c r="G5" t="n">
-        <v>4.6675</v>
+        <v>8.7944</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8533</v>
+        <v>6.5316</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8142</v>
+        <v>2.2629</v>
       </c>
       <c r="J5" t="n">
-        <v>9.7537</v>
+        <v>13.1923</v>
       </c>
       <c r="K5" t="n">
-        <v>3.9977</v>
+        <v>7.8415</v>
       </c>
       <c r="L5" t="n">
-        <v>5.756</v>
+        <v>5.3508</v>
       </c>
       <c r="M5" t="n">
-        <v>-5.0862</v>
+        <v>-4.3979</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.1444</v>
+        <v>-1.3101</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.9418</v>
+        <v>-3.0878</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.3369</v>
+        <v>-3.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>-8.958</v>
+        <v>-12.0736</v>
       </c>
       <c r="R5" t="n">
-        <v>6.6211</v>
+        <v>8.3736</v>
       </c>
       <c r="S5" t="n">
-        <v>6.1276</v>
+        <v>2.3112</v>
       </c>
       <c r="T5" t="n">
-        <v>1.1731</v>
+        <v>1.6604</v>
       </c>
       <c r="U5" t="n">
-        <v>4.9545</v>
+        <v>0.651</v>
       </c>
       <c r="V5" t="n">
-        <v>3.6115</v>
+        <v>6.4363</v>
       </c>
       <c r="W5" t="n">
-        <v>7.9069</v>
+        <v>6.0537</v>
       </c>
       <c r="X5" t="n">
-        <v>-4.2954</v>
+        <v>0.3826</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. BOTAS FERNANDEZ</t>
+          <t>D. JUZBASIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>9.289899999999999</v>
+        <v>8.8499</v>
       </c>
       <c r="E6" t="n">
-        <v>5.6192</v>
+        <v>9.339600000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>3.6707</v>
+        <v>-0.4896000000000003</v>
       </c>
       <c r="G6" t="n">
-        <v>8.7944</v>
+        <v>4.6675</v>
       </c>
       <c r="H6" t="n">
-        <v>6.5316</v>
+        <v>1.8533</v>
       </c>
       <c r="I6" t="n">
-        <v>2.2629</v>
+        <v>2.8142</v>
       </c>
       <c r="J6" t="n">
-        <v>13.1923</v>
+        <v>9.7537</v>
       </c>
       <c r="K6" t="n">
-        <v>7.8415</v>
+        <v>3.9977</v>
       </c>
       <c r="L6" t="n">
-        <v>5.3508</v>
+        <v>5.756</v>
       </c>
       <c r="M6" t="n">
-        <v>-4.3979</v>
+        <v>-5.0862</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.3101</v>
+        <v>-2.1444</v>
       </c>
       <c r="O6" t="n">
-        <v>-3.0878</v>
+        <v>-2.9418</v>
       </c>
       <c r="P6" t="n">
-        <v>-3.7</v>
+        <v>-2.3369</v>
       </c>
       <c r="Q6" t="n">
-        <v>-12.0736</v>
+        <v>-8.958</v>
       </c>
       <c r="R6" t="n">
-        <v>8.3736</v>
+        <v>6.6211</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.2409</v>
+        <v>2.9076</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.5532</v>
+        <v>0.6368999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6878000000000001</v>
+        <v>2.2707</v>
       </c>
       <c r="V6" t="n">
-        <v>6.4363</v>
+        <v>3.6115</v>
       </c>
       <c r="W6" t="n">
-        <v>6.0537</v>
+        <v>7.9069</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3826</v>
+        <v>-4.2954</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>8.2784</v>
+        <v>5.9754</v>
       </c>
       <c r="E7" t="n">
-        <v>9.3597</v>
+        <v>7.8886</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0813</v>
+        <v>-1.9131</v>
       </c>
       <c r="G7" t="n">
         <v>6.3305</v>
@@ -1000,13 +1000,13 @@
         <v>4.6736</v>
       </c>
       <c r="S7" t="n">
-        <v>5.2921</v>
+        <v>2.9891</v>
       </c>
       <c r="T7" t="n">
-        <v>2.3508</v>
+        <v>0.8796000000000002</v>
       </c>
       <c r="U7" t="n">
-        <v>2.9414</v>
+        <v>2.1096</v>
       </c>
       <c r="V7" t="n">
         <v>-3.7337</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. JIMENEZ EXPOSITO</t>
+          <t>J. CEBOLLA HERRERA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,70 +1264,70 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.632</v>
+        <v>-0.3632999999999997</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.7675999999999999</v>
+        <v>1.5904</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1357</v>
+        <v>-1.9536</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.7834</v>
+        <v>2.6735</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0205</v>
+        <v>-0.1194</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.804</v>
+        <v>2.7927</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.644</v>
+        <v>3.4522</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0205</v>
+        <v>1.2778</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6645</v>
+        <v>2.1742</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1395</v>
+        <v>-0.7785</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>-1.3971</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1395</v>
+        <v>0.6185</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3895</v>
+        <v>-1.3632</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-3.8948</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3895</v>
+        <v>2.5315</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.238</v>
+        <v>-0.9409</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1237</v>
+        <v>-0.6885</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1144</v>
+        <v>-0.2526</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.7326999999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.7216</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-3.4542</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.4231</v>
+        <v>-0.5830000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.6568</v>
+        <v>-2.2341</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2337</v>
+        <v>1.6512</v>
       </c>
       <c r="G12" t="n">
         <v>-1.2834</v>
@@ -1390,13 +1390,13 @@
         <v>4.4789</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0509</v>
+        <v>-0.2106</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7245</v>
+        <v>-0.3017</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3262999999999999</v>
+        <v>0.09099999999999997</v>
       </c>
       <c r="V12" t="n">
         <v>0.7163</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. CEBOLLA HERRERA</t>
+          <t>D. JIMENEZ EXPOSITO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,70 +1420,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.5638</v>
+        <v>-0.6042</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1331999999999995</v>
+        <v>-0.7675999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.6971</v>
+        <v>0.1635</v>
       </c>
       <c r="G13" t="n">
-        <v>2.6735</v>
+        <v>-0.7834</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.1194</v>
+        <v>0.0205</v>
       </c>
       <c r="I13" t="n">
-        <v>2.7927</v>
+        <v>-0.804</v>
       </c>
       <c r="J13" t="n">
-        <v>3.4522</v>
+        <v>-0.644</v>
       </c>
       <c r="K13" t="n">
-        <v>1.2778</v>
+        <v>0.0205</v>
       </c>
       <c r="L13" t="n">
-        <v>2.1742</v>
+        <v>-0.6645</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.7785</v>
+        <v>-0.1395</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.3971</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6185</v>
+        <v>-0.1395</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.3632</v>
+        <v>0.3895</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.8948</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.5315</v>
+        <v>0.3895</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.1415</v>
+        <v>-0.2102</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.1457</v>
+        <v>-0.1237</v>
       </c>
       <c r="U13" t="n">
-        <v>0.00430000000000004</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.7326999999999999</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>2.7216</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.4542</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.391</v>
+        <v>-0.6932000000000003</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.0882</v>
+        <v>0.5307000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.3027</v>
+        <v>-1.2239</v>
       </c>
       <c r="G14" t="n">
         <v>-4.7278</v>
@@ -1546,13 +1546,13 @@
         <v>3.7</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.5099</v>
+        <v>0.1877</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8168000000000001</v>
+        <v>0.802</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.6932</v>
+        <v>-0.6143</v>
       </c>
       <c r="V14" t="n">
         <v>4.431</v>
@@ -1579,13 +1579,13 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>-4.5162</v>
+        <v>-1.386500000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>-7.6769</v>
+        <v>-5.7591</v>
       </c>
       <c r="F15" t="n">
-        <v>3.1607</v>
+        <v>4.3727</v>
       </c>
       <c r="G15" t="n">
         <v>-4.6616</v>
@@ -1624,13 +1624,13 @@
         <v>7.7895</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.739</v>
+        <v>2.3909</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.05430000000000001</v>
+        <v>1.8635</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6846</v>
+        <v>0.5273</v>
       </c>
       <c r="V15" t="n">
         <v>2.4422</v>
@@ -1657,13 +1657,13 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>-20.4885</v>
+        <v>-17.9182</v>
       </c>
       <c r="E16" t="n">
-        <v>-19.2868</v>
+        <v>-17.7677</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.2016</v>
+        <v>-0.1504</v>
       </c>
       <c r="G16" t="n">
         <v>-14.6878</v>
@@ -1702,13 +1702,13 @@
         <v>5.2578</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.7573</v>
+        <v>-0.1872000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0704</v>
+        <v>0.4486</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.6869</v>
+        <v>-0.6357</v>
       </c>
       <c r="V16" t="n">
         <v>-0.1221000000000001</v>
@@ -1735,16 +1735,16 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>59.51019999999998</v>
+        <v>63.4046</v>
       </c>
       <c r="E17" t="n">
-        <v>54.24499999999999</v>
+        <v>55.4816</v>
       </c>
       <c r="F17" t="n">
-        <v>5.265300000000001</v>
+        <v>7.923900000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>22.67809999999999</v>
+        <v>22.6781</v>
       </c>
       <c r="H17" t="n">
         <v>9.790400000000002</v>
@@ -1762,7 +1762,7 @@
         <v>28.7864</v>
       </c>
       <c r="M17" t="n">
-        <v>-38.3612</v>
+        <v>-38.36120000000001</v>
       </c>
       <c r="N17" t="n">
         <v>-22.4631</v>
@@ -1780,19 +1780,19 @@
         <v>64.26300000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>15.3482</v>
+        <v>19.2426</v>
       </c>
       <c r="T17" t="n">
-        <v>10.5872</v>
+        <v>11.8232</v>
       </c>
       <c r="U17" t="n">
-        <v>4.761700000000001</v>
+        <v>7.419400000000001</v>
       </c>
       <c r="V17" t="n">
         <v>30.2469</v>
       </c>
       <c r="W17" t="n">
-        <v>55.64470000000001</v>
+        <v>55.6447</v>
       </c>
       <c r="X17" t="n">
         <v>-25.3982</v>
